--- a/pages/bread_data.xlsx
+++ b/pages/bread_data.xlsx
@@ -425,41 +425,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>ImageRelative</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>ImageAbsolute</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Production Day</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Expiry</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ordering Lead Time</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Remark/Update (If Any)</t>
         </is>
@@ -468,163 +473,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>????</t>
+          <t>static/images/bread_bj_butterscotch_loaf_(360g_pkt).png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sourdough</t>
+          <t>C:\Users\YeeGin.Woon\Bread\pages\static\images\bread_bj_butterscotch_loaf_(360g_pkt).png</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Local Mill</t>
+          <t>BREAD BJ BUTTERSCOTCH LOAF (360G/PKT)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wednesday, Friday</t>
+          <t>Gardenia</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Production Day + 5 days</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Baguette</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>French Bakery</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+          <t>Tuesday, Friday</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Production Day + 4 days</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>4 days, 12pm cut-off</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>hellp</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Production Day + 5 days</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0 days</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Gardenia Wrap</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>gard</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Saturday, Friday, Wednesday</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Production Day + 6 days</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>5 days, 10:39 AM cut-off</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>/static/images/hotdog.jpeg</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>hotdog</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>gardenia</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Production Day + 5 days</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5 days, 12:15 AM cut-off</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>please see</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/pages/bread_data.xlsx
+++ b/pages/bread_data.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tuesday, Friday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0 days</t>
+          <t>3 days</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/pages/bread_data.xlsx
+++ b/pages/bread_data.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3 days</t>
+          <t>4 days, 01:15 AM cut-off</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/pages/bread_data.xlsx
+++ b/pages/bread_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,15 +456,30 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Expiry Days</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Expiry</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Lead Day</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Lead Time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ordering Lead Time</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Remark/Update (If Any)</t>
         </is>
@@ -473,40 +488,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>static/images/bread_bj_butterscotch_loaf_(360g_pkt).png</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>C:\Users\YeeGin.Woon\Bread\pages\static\images\bread_bj_butterscotch_loaf_(360g_pkt).png</t>
-        </is>
-      </c>
+          <t>🍞</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BREAD BJ BUTTERSCOTCH LOAF (360G/PKT)</t>
+          <t>Baguette</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gardenia</t>
+          <t>hello</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Production Day + 4 days</t>
-        </is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4 days, 01:15 AM cut-off</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Production Day + 2 days</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>00:15:00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5 days, 00:15:00 cut-off</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>static/images/butter.png</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C:\Users\YeeGin.Woon\Bread\pages\static\images\butter.png</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>butter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Saturday, Thursday</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Production Day + 5 days</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0 days</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
